--- a/위니온.xlsx
+++ b/위니온.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rainpsy\.gemini\antigravity-ide\scratch\cj-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247E080B-6A7B-47A7-8864-DDAC7636D536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91837270-DB99-4C21-8533-80ECE70E7DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6304" uniqueCount="1478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6302" uniqueCount="1476">
   <si>
     <t>접수번호</t>
   </si>
@@ -4453,14 +4453,6 @@
   </si>
   <si>
     <t>스마트윈드 출하</t>
-  </si>
-  <si>
-    <t>누가5야?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5대5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4959,8 +4951,8 @@
       <c r="P2" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" t="s">
-        <v>1476</v>
+      <c r="Q2">
+        <v>1818</v>
       </c>
       <c r="R2" t="s">
         <v>31</v>
@@ -5015,8 +5007,8 @@
       <c r="P3" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" t="s">
-        <v>1477</v>
+      <c r="Q3">
+        <v>1818</v>
       </c>
       <c r="R3" t="s">
         <v>31</v>
@@ -30058,7 +30050,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R1 A4:R450 A2:P2 R2 A3:P3 R3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R1 A5:R450 A2:P2 R2 A3:P3 R3 A4:P4 R4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/위니온.xlsx
+++ b/위니온.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rainpsy\.gemini\antigravity-ide\scratch\cj-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCC2DDC-E194-45A8-A349-0A4D28ADF549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C459BA47-F834-421A-832C-D08ACA941A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15278" uniqueCount="3310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15278" uniqueCount="3311">
   <si>
     <t>접수번호</t>
   </si>
@@ -9956,6 +9956,10 @@
   </si>
   <si>
     <t>틀로드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JM컴퍼니</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10621,7 +10625,7 @@
         <v>29</v>
       </c>
       <c r="Q5" t="s">
-        <v>30</v>
+        <v>3310</v>
       </c>
       <c r="R5" t="s">
         <v>31</v>
@@ -71447,7 +71451,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R1 A5:R1091 A2:P2 R2 A3:P3 R3 A4:P4 R4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R1 A6:R1091 A2:P2 R2 A3:P3 R3 A4:P4 R4 A5:P5 R5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/위니온.xlsx
+++ b/위니온.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rainpsy\.gemini\antigravity-ide\scratch\cj-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6BFF72-785A-49B5-B154-41DC094F50A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA7E98B-257C-4424-9C7E-4FBDF18B91A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10352,6 +10352,8 @@
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -70772,7 +70774,7 @@
         <v>29</v>
       </c>
       <c r="Q1079" t="s">
-        <v>30</v>
+        <v>3308</v>
       </c>
       <c r="R1079" t="s">
         <v>31</v>
@@ -70828,7 +70830,7 @@
         <v>29</v>
       </c>
       <c r="Q1080" t="s">
-        <v>30</v>
+        <v>3309</v>
       </c>
       <c r="R1080" t="s">
         <v>31</v>
@@ -70884,7 +70886,7 @@
         <v>29</v>
       </c>
       <c r="Q1081" t="s">
-        <v>30</v>
+        <v>3308</v>
       </c>
       <c r="R1081" t="s">
         <v>31</v>
@@ -70940,7 +70942,7 @@
         <v>29</v>
       </c>
       <c r="Q1082" t="s">
-        <v>30</v>
+        <v>3310</v>
       </c>
       <c r="R1082" t="s">
         <v>31</v>
@@ -71454,7 +71456,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R1 A6:R1091 A2:P2 R2 A3:P3 R3 A4:P4 R4 A5:P5 R5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R1 A6:R1078 A2:P2 R2 A3:P3 R3 A4:P4 R4 A5:P5 R5 A1083:R1091 A1079:P1082 R1079:R1082" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>